--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,720 +3465,6 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ASO Chlef</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>46093.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bragantino</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="3" t="n">
         <v>46093.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -668,13 +668,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46093.3125</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -677,10 +677,10 @@
         <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
         <v>2.28</v>
@@ -689,13 +689,13 @@
         <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.18</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46093.41666666666</v>
@@ -906,64 +906,64 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46093.4375</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46093.58333333334</v>
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>3.99</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.66</v>
+        <v>2.87</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.87</v>
+        <v>3.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.62</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2334,64 +2334,64 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2334,64 +2334,64 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,64 +2453,64 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.12</v>
+        <v>3.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.77</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,64 +2453,64 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2685,70 +2685,70 @@
         <v>3.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46093.79166666666</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.77</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46093.8125</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.45</v>
+        <v>7.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7.52</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46093.83333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="N25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46093.89583333334</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -671,22 +671,22 @@
         <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
         <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
         <v>5.9</v>
@@ -698,34 +698,34 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AG2" t="n">
         <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46093.3125</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
         <v>3.5</v>
@@ -787,13 +787,13 @@
         <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.3</v>
@@ -802,13 +802,13 @@
         <v>3.08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
@@ -817,34 +817,34 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46093.41666666666</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
@@ -927,34 +927,34 @@
         <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
         <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
         <v>3.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
         <v>2.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
         <v>2.2</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
         <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.53</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46093.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2096,64 +2096,64 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2218,40 +2218,40 @@
         <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
         <v>3.66</v>
       </c>
       <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.36</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
         <v>1.82</v>
@@ -2266,10 +2266,10 @@
         <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>1.53</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="O18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>6.55</v>
+        <v>5.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46093.66666666666</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -725,7 +725,7 @@
         <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46093.3125</v>
@@ -787,7 +787,7 @@
         <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="P3" t="n">
         <v>2.26</v>
@@ -805,7 +805,7 @@
         <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
         <v>5.75</v>
@@ -820,7 +820,7 @@
         <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.68</v>
+        <v>3.87</v>
       </c>
       <c r="AA3" t="n">
         <v>1.73</v>
@@ -844,7 +844,7 @@
         <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46093.41666666666</v>
@@ -1299,7 +1299,7 @@
         <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB7" t="n">
         <v>2.04</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2096,64 +2096,64 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>5.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>5.85</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46093.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>5.85</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,64 +2453,64 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46093.66666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>5.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46093.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:BI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,125 +488,255 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Goals_H_2T</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Goals_A_2T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_H</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_A</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_FT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_FT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_FT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_HT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under25</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over45</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under45</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_A</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_75</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_85</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_95</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_105</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_115</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_75</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_85</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_95</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_105</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_115</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over05</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over15</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under05</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under15</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under25</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -653,81 +783,159 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.35</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>2.19</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
         <v>3.8</v>
       </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
         <v>1.33</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>3.17</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
         <v>2.67</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>1.44</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>5.9</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
         <v>1.07</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AC2" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AD2" t="n">
         <v>3.58</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AE2" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AF2" t="n">
         <v>2.02</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
         <v>2.81</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AI2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.68</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
         <v>2.04</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AM2" t="n">
         <v>1.21</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AN2" t="n">
         <v>1.7</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="3" t="n">
         <v>46093.3125</v>
       </c>
     </row>
@@ -772,81 +980,159 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>3.25</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>3.5</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>1.91</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>4.04</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
         <v>2.5</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>1.32</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>3.08</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
         <v>2.5</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
         <v>1.44</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
         <v>5.75</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>1.07</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AC3" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AD3" t="n">
         <v>3.68</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
         <v>1.99</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
         <v>2.74</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AL3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AM3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AN3" t="n">
         <v>1.23</v>
       </c>
-      <c r="AI3" s="3" t="n">
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="3" t="n">
         <v>46093.41666666666</v>
       </c>
     </row>
@@ -891,81 +1177,159 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.34</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="U4" t="n">
         <v>2.87</v>
       </c>
-      <c r="R4" t="n">
+      <c r="V4" t="n">
         <v>1.28</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>3.12</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>2.5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
         <v>1.43</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
         <v>6</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>1.06</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>3.88</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
         <v>1.74</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>2.06</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
         <v>2.74</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AL4" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AM4" t="n">
         <v>1.22</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AN4" t="n">
         <v>1.37</v>
       </c>
-      <c r="AI4" s="3" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="3" t="n">
         <v>46093.4375</v>
       </c>
     </row>
@@ -1010,23 +1374,23 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -1084,7 +1448,85 @@
       <c r="AH5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="3" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="3" t="n">
         <v>46093.47916666666</v>
       </c>
     </row>
@@ -1129,23 +1571,23 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
@@ -1203,7 +1645,85 @@
       <c r="AH6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" s="3" t="n">
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="3" t="n">
         <v>46093.5</v>
       </c>
     </row>
@@ -1248,81 +1768,159 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>1.44</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>5.75</v>
       </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
         <v>1.94</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>1.31</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>3.02</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>2.47</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>1.45</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
         <v>5.55</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
         <v>1.08</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AC7" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AD7" t="n">
         <v>3.8</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
         <v>1.71</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AF7" t="n">
         <v>2.04</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AG7" t="n">
         <v>2.62</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
         <v>1.38</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AI7" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AL7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AM7" t="n">
         <v>1.15</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AN7" t="n">
         <v>2.53</v>
       </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3" t="n">
         <v>46093.58333333334</v>
       </c>
     </row>
@@ -1367,23 +1965,23 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1441,7 +2039,85 @@
       <c r="AH8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" s="3" t="n">
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="3" t="n">
         <v>46093.60416666666</v>
       </c>
     </row>
@@ -1486,23 +2162,23 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1560,7 +2236,85 @@
       <c r="AH9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="3" t="n">
         <v>46093.60416666666</v>
       </c>
     </row>
@@ -1605,23 +2359,23 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +2433,85 @@
       <c r="AH10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="3" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
         <v>46093.61458333334</v>
       </c>
     </row>
@@ -1724,23 +2556,23 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1798,7 +2630,85 @@
       <c r="AH11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="3" t="n">
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3" t="n">
         <v>46093.625</v>
       </c>
     </row>
@@ -1843,23 +2753,23 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1917,7 +2827,85 @@
       <c r="AH12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="3" t="n">
         <v>46093.625</v>
       </c>
     </row>
@@ -1962,81 +2950,159 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.85</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
         <v>3.66</v>
       </c>
-      <c r="R13" t="n">
+      <c r="V13" t="n">
         <v>1.35</v>
       </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
         <v>2.9</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
         <v>2.77</v>
       </c>
-      <c r="U13" t="n">
+      <c r="Y13" t="n">
         <v>1.36</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Z13" t="n">
         <v>7</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AD13" t="n">
         <v>3.38</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AE13" t="n">
         <v>1.77</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AF13" t="n">
         <v>1.82</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AG13" t="n">
         <v>3.22</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AH13" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AI13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AL13" t="n">
         <v>2</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AM13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AN13" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI13" s="3" t="n">
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2081,81 +3147,159 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>2.4</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>3.5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>2.63</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>3.03</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
+      <c r="V14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
         <v>2.91</v>
       </c>
-      <c r="T14" t="n">
+      <c r="X14" t="n">
         <v>2.62</v>
       </c>
-      <c r="U14" t="n">
+      <c r="Y14" t="n">
         <v>1.4</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Z14" t="n">
         <v>6.55</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AD14" t="n">
         <v>3.68</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AE14" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AF14" t="n">
         <v>1.99</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
         <v>3</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AH14" t="n">
         <v>1.38</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AI14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.61</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AL14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AM14" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AN14" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI14" s="3" t="n">
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2200,81 +3344,159 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.55</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
         <v>2.75</v>
       </c>
-      <c r="R15" t="n">
+      <c r="V15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
+      <c r="W15" t="n">
         <v>2.62</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="n">
         <v>3.02</v>
       </c>
-      <c r="U15" t="n">
+      <c r="Y15" t="n">
         <v>1.31</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Z15" t="n">
         <v>8.1</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AA15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AB15" t="n">
         <v>1</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AC15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AD15" t="n">
         <v>3.15</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AE15" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AF15" t="n">
         <v>1.71</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AG15" t="n">
         <v>3.85</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AH15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AI15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AL15" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AM15" t="n">
         <v>1.65</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AN15" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI15" s="3" t="n">
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2319,23 +3541,23 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -2393,7 +3615,85 @@
       <c r="AH16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2438,23 +3738,23 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
@@ -2512,7 +3812,85 @@
       <c r="AH17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2557,81 +3935,159 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="P18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
+      <c r="V18" t="n">
         <v>1.32</v>
       </c>
-      <c r="S18" t="n">
+      <c r="W18" t="n">
         <v>2.96</v>
       </c>
-      <c r="T18" t="n">
+      <c r="X18" t="n">
         <v>2.5</v>
       </c>
-      <c r="U18" t="n">
+      <c r="Y18" t="n">
         <v>1.43</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Z18" t="n">
         <v>5.85</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
         <v>1.1</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AC18" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AD18" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AF18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AG18" t="n">
         <v>2.88</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AH18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AI18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.6</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AL18" t="n">
         <v>2.14</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AM18" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AN18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
         <v>46093.66666666666</v>
       </c>
     </row>
@@ -2676,81 +4132,159 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.02</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AN19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI19" s="3" t="n">
+      <c r="AR19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="3" t="n">
         <v>46093.79166666666</v>
       </c>
     </row>
@@ -2795,81 +4329,159 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>3.1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD20" t="n">
         <v>3.5</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="AE20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.36</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.38</v>
       </c>
-      <c r="V20" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AZ20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="BC20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI20" s="3" t="n">
+      <c r="BF20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
         <v>46093.8125</v>
       </c>
     </row>
@@ -2914,81 +4526,159 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="P21" t="n">
         <v>1.4</v>
       </c>
-      <c r="M21" t="n">
+      <c r="Q21" t="n">
         <v>4.5</v>
       </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
         <v>7.75</v>
       </c>
-      <c r="O21" t="n">
+      <c r="S21" t="n">
         <v>1.9</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>7.52</v>
       </c>
-      <c r="R21" t="n">
+      <c r="V21" t="n">
         <v>1.35</v>
       </c>
-      <c r="S21" t="n">
+      <c r="W21" t="n">
         <v>2.94</v>
       </c>
-      <c r="T21" t="n">
+      <c r="X21" t="n">
         <v>2.62</v>
       </c>
-      <c r="U21" t="n">
+      <c r="Y21" t="n">
         <v>1.43</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Z21" t="n">
         <v>6.25</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AA21" t="n">
         <v>1.06</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="BC21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.73</v>
       </c>
-      <c r="AG21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI21" s="3" t="n">
+      <c r="BF21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="3" t="n">
         <v>46093.83333333334</v>
       </c>
     </row>
@@ -3033,23 +4723,23 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +4797,85 @@
       <c r="AH22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="n">
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
         <v>46093.875</v>
       </c>
     </row>
@@ -3152,23 +4920,23 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
@@ -3226,7 +4994,85 @@
       <c r="AH23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="3" t="n">
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
         <v>46093.875</v>
       </c>
     </row>
@@ -3271,23 +5117,23 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -3345,7 +5191,85 @@
       <c r="AH24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
         <v>46093.875</v>
       </c>
     </row>
@@ -3390,81 +5314,159 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.78</v>
       </c>
-      <c r="N25" t="n">
+      <c r="R25" t="n">
         <v>3.45</v>
       </c>
-      <c r="O25" t="n">
+      <c r="S25" t="n">
         <v>2.6</v>
       </c>
-      <c r="P25" t="n">
+      <c r="T25" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="U25" t="n">
         <v>3.75</v>
       </c>
-      <c r="R25" t="n">
+      <c r="V25" t="n">
         <v>1.33</v>
       </c>
-      <c r="S25" t="n">
+      <c r="W25" t="n">
         <v>3.04</v>
       </c>
-      <c r="T25" t="n">
+      <c r="X25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT25" t="n">
         <v>2.8</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AU25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.38</v>
       </c>
-      <c r="V25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AZ25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
         <v>46093.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -846,10 +846,10 @@
         <v>3.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
         <v>2.81</v>
@@ -864,7 +864,7 @@
         <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL2" t="n">
         <v>2.04</v>
@@ -873,7 +873,7 @@
         <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF2" t="n">
         <v>1.18</v>
@@ -998,28 +998,28 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>4.04</v>
+        <v>3.87</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
@@ -1034,7 +1034,7 @@
         <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
         <v>1.18</v>
@@ -1043,13 +1043,13 @@
         <v>3.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AF3" t="n">
         <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
         <v>1.4</v>
@@ -1064,13 +1064,13 @@
         <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AM3" t="n">
         <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="R7" t="n">
-        <v>5.75</v>
+        <v>6.24</v>
       </c>
       <c r="S7" t="n">
         <v>1.94</v>
@@ -1831,7 +1831,7 @@
         <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
         <v>2.04</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
         <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.15</v>
+        <v>5.32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
         <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AV13" t="n">
         <v>2.45</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.03</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
         <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.33</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD14" t="n">
-        <v>3.68</v>
+        <v>2.97</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AW14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AZ14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BC14" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,124 +3371,124 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.75</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="AU15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.65</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS15" t="n">
+      <c r="BA15" t="n">
         <v>2.55</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>2.15</v>
       </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="BA13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BC13" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE13" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,124 +3174,124 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,124 +3371,124 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,124 +3765,124 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
         <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="X16" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
         <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.32</v>
+        <v>6.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
         <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV16" t="n">
         <v>2.45</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.36</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AI17" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,124 +3371,124 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3568,124 +3568,124 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,52 +3837,52 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2977,124 +2977,124 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,124 +3765,124 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3959,16 +3959,16 @@
         <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V18" t="n">
         <v>1.32</v>
@@ -3977,7 +3977,7 @@
         <v>2.96</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Y18" t="n">
         <v>1.43</v>
@@ -3986,28 +3986,28 @@
         <v>5.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" t="n">
         <v>5.25</v>
@@ -4025,7 +4025,7 @@
         <v>1.24</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>1.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BD18" t="n">
         <v>3.82</v>
@@ -4150,61 +4150,61 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.1</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U19" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>2.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>1.29</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
         <v>6.5</v>
@@ -4216,13 +4216,13 @@
         <v>1.75</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AM19" t="n">
         <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4258,10 +4258,10 @@
         <v>1.54</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BB19" t="n">
         <v>1.25</v>
@@ -4270,7 +4270,7 @@
         <v>2.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="BE19" t="n">
         <v>1.65</v>
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="V20" t="n">
         <v>1.36</v>
@@ -4377,28 +4377,28 @@
         <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="AA20" t="n">
         <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
         <v>3.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
         <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="n">
         <v>1.33</v>
@@ -4407,19 +4407,19 @@
         <v>5.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL20" t="n">
         <v>2</v>
       </c>
       <c r="AM20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.36</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>3.49</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AW20" t="n">
         <v>1.98</v>
@@ -4455,10 +4455,10 @@
         <v>1.38</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
         <v>1.22</v>
@@ -4467,13 +4467,13 @@
         <v>2.05</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="R21" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="S21" t="n">
         <v>1.9</v>
@@ -4580,25 +4580,25 @@
         <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
         <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
         <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
         <v>5.75</v>
@@ -4610,40 +4610,40 @@
         <v>1.91</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AM21" t="n">
         <v>1.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AT21" t="n">
         <v>3.05</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AX21" t="n">
         <v>1.52</v>
@@ -4652,10 +4652,10 @@
         <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BB21" t="n">
         <v>1.22</v>
@@ -4664,10 +4664,10 @@
         <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BF21" t="n">
         <v>1.18</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5332,16 +5332,16 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
         <v>3.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
         <v>2.24</v>
@@ -5350,16 +5350,16 @@
         <v>3.75</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="X25" t="n">
         <v>2.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
         <v>7.3</v>
@@ -5368,31 +5368,31 @@
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.95</v>
+        <v>6.52</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
         <v>1.77</v>
@@ -5404,13 +5404,13 @@
         <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.44</v>
@@ -5425,7 +5425,7 @@
         <v>2.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="AV25" t="n">
         <v>2.58</v>
@@ -5440,7 +5440,7 @@
         <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="BA25" t="n">
         <v>2.53</v>
@@ -5449,7 +5449,7 @@
         <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BD25" t="n">
         <v>3.4</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -816,19 +816,19 @@
         <v>2.19</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="X2" t="n">
         <v>2.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
         <v>5.9</v>
@@ -846,7 +846,7 @@
         <v>3.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
@@ -864,7 +864,7 @@
         <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
         <v>2.04</v>
@@ -915,13 +915,13 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
         <v>1.97</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="BE2" t="n">
         <v>1.74</v>
@@ -998,31 +998,31 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
         <v>2.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Y3" t="n">
         <v>1.44</v>
@@ -1037,13 +1037,13 @@
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
         <v>1.99</v>
@@ -1052,19 +1052,19 @@
         <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.29</v>
+        <v>5.05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
         <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AM3" t="n">
         <v>1.2</v>
@@ -1115,7 +1115,7 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BD3" t="n">
         <v>3.98</v>
@@ -1124,7 +1124,7 @@
         <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1204,13 +1204,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="T4" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="V4" t="n">
         <v>1.28</v>
@@ -1225,7 +1225,7 @@
         <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AA4" t="n">
         <v>1.06</v>
@@ -1237,13 +1237,13 @@
         <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.88</v>
+        <v>3.99</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
         <v>2.74</v>
@@ -1252,7 +1252,7 @@
         <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.03</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>6.24</v>
+        <v>5.75</v>
       </c>
       <c r="S7" t="n">
         <v>1.94</v>
@@ -1801,19 +1801,19 @@
         <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>6.27</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
         <v>5.55</v>
@@ -1831,7 +1831,7 @@
         <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AF7" t="n">
         <v>2.04</v>
@@ -1843,7 +1843,7 @@
         <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.97</v>
+        <v>4.7</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.12</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
         <v>3.66</v>
@@ -3389,46 +3389,46 @@
         <v>2.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
         <v>3.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AH15" t="n">
         <v>1.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AM15" t="n">
         <v>1.25</v>
@@ -3479,7 +3479,7 @@
         <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
         <v>3.72</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3765,70 +3765,70 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
         <v>2.62</v>
       </c>
       <c r="X17" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD17" t="n">
         <v>2.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.03</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>1.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
         <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF17" t="n">
         <v>1.1</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1204,19 +1204,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="X4" t="n">
         <v>2.5</v>
@@ -1234,25 +1234,25 @@
         <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1267,7 +1267,7 @@
         <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BD4" t="n">
         <v>4.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
         <v>1.17</v>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,83 +2964,83 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46093.66666666666</v>
+        <v>46093.64583333334</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46093.66666666666</v>
+        <v>46093.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46093.66666666666</v>
+        <v>46093.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,124 +3765,124 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.31</v>
+        <v>2.85</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>2.7</v>
+        <v>3.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="X19" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
         <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AR19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>1.65</v>
       </c>
-      <c r="AS19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BA19" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC19" t="n">
         <v>2.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="BE19" t="n">
         <v>1.65</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46093.79166666666</v>
+        <v>46093.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46093.8125</v>
+        <v>46093.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>7.52</v>
+        <v>3.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Y21" t="n">
         <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.79</v>
+        <v>1.43</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AR21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AS21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.35</v>
+        <v>2.04</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BE21" t="n">
         <v>1.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46093.83333333334</v>
+        <v>46093.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46093.875</v>
+        <v>46093.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,137 +4934,137 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46093.875</v>
+        <v>46093.8125</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>7.52</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46093.875</v>
+        <v>46093.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,145 +5328,736 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>46093.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
+        <v>46093.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
+        <v>46093.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q28" t="n">
         <v>3.4</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R28" t="n">
         <v>3.45</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S28" t="n">
         <v>2.63</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T28" t="n">
         <v>2.24</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U28" t="n">
         <v>3.75</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V28" t="n">
         <v>1.34</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W28" t="n">
         <v>2.99</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X28" t="n">
         <v>2.85</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y28" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z28" t="n">
         <v>7.3</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA28" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB28" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AD28" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AE28" t="n">
         <v>2</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG28" t="n">
         <v>3.5</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH28" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AI28" t="n">
         <v>6.52</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AJ28" t="n">
         <v>1.04</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AK28" t="n">
         <v>1.77</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AL28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AM28" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AN28" t="n">
         <v>1.75</v>
       </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AQ28" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AR28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AS28" t="n">
         <v>2.16</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AT28" t="n">
         <v>2.8</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AU28" t="n">
         <v>3.51</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV28" t="n">
         <v>2.58</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AW28" t="n">
         <v>1.99</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AX28" t="n">
         <v>1.62</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AY28" t="n">
         <v>1.38</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="AZ28" t="n">
         <v>1.68</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BA28" t="n">
         <v>2.53</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB28" t="n">
         <v>1.25</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BC28" t="n">
         <v>2.2</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BD28" t="n">
         <v>3.4</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BE28" t="n">
         <v>1.62</v>
       </c>
-      <c r="BF25" t="n">
+      <c r="BF28" t="n">
         <v>1.15</v>
       </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="3" t="n">
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
         <v>46093.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -810,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.19</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.32</v>
@@ -825,7 +825,7 @@
         <v>2.96</v>
       </c>
       <c r="X2" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="Y2" t="n">
         <v>1.42</v>
@@ -846,28 +846,28 @@
         <v>3.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.1</v>
+        <v>5.42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AM2" t="n">
         <v>1.21</v>
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="S3" t="n">
         <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
         <v>2.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
         <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
         <v>1.07</v>
@@ -1037,10 +1037,10 @@
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
         <v>1.76</v>
@@ -1049,13 +1049,13 @@
         <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
@@ -1064,13 +1064,13 @@
         <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,13 +1115,13 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
         <v>3.98</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
         <v>1.18</v>
@@ -1786,34 +1786,34 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>6.27</v>
+        <v>4.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="X7" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
         <v>5.55</v>
@@ -1822,7 +1822,7 @@
         <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
         <v>1.19</v>
@@ -1831,19 +1831,19 @@
         <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
         <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.7</v>
+        <v>4.97</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.12</v>
@@ -1852,13 +1852,13 @@
         <v>1.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,16 +1903,16 @@
         <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BD7" t="n">
         <v>4.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.67</v>
+        <v>6.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>6.25</v>
+        <v>2.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
         <v>3.35</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="AU16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>2.15</v>
       </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="BA16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BD16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.56</v>
       </c>
-      <c r="AY16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,124 +3765,124 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4159,124 +4159,124 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4356,124 +4356,124 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
@@ -1231,7 +1231,7 @@
         <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
         <v>1.18</v>
@@ -1240,7 +1240,7 @@
         <v>3.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="S14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.85</v>
+        <v>6.55</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
         <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AV17" t="n">
         <v>2.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="X18" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AM18" t="n">
         <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV18" t="n">
         <v>2.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BA18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC18" t="n">
         <v>2.1</v>
       </c>
-      <c r="BB18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,52 +4231,52 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,52 +4625,52 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,64 +4741,64 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>4.31</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="X22" t="n">
         <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>6.93</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.1</v>
@@ -4819,52 +4819,52 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR22" t="n">
         <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.34</v>
+        <v>4.55</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF22" t="n">
         <v>1.17</v>
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
         <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X23" t="n">
         <v>2.65</v>
@@ -4974,7 +4974,7 @@
         <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
         <v>1.25</v>
@@ -4986,76 +4986,76 @@
         <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AH23" t="n">
         <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.49</v>
+        <v>3.72</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AW23" t="n">
         <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD23" t="n">
         <v>3.8</v>
@@ -5135,37 +5135,37 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
         <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>7.52</v>
+        <v>8.15</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
@@ -5174,82 +5174,82 @@
         <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>2.05</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5923,49 +5923,49 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="S28" t="n">
         <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA28" t="n">
         <v>1.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5974,67 +5974,67 @@
         <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.52</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.04</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
         <v>1.95</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
@@ -6046,7 +6046,7 @@
         <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
         <v>1.15</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S2" t="n">
         <v>2.4</v>
@@ -846,28 +846,28 @@
         <v>3.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.42</v>
+        <v>5.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
         <v>1.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AM2" t="n">
         <v>1.21</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
         <v>3.8</v>
@@ -1013,7 +1013,7 @@
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1043,7 +1043,7 @@
         <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
         <v>1.99</v>
@@ -1055,7 +1055,7 @@
         <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.14</v>
@@ -1213,10 +1213,10 @@
         <v>2.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="X4" t="n">
         <v>2.5</v>
@@ -1231,16 +1231,16 @@
         <v>1.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
@@ -1252,7 +1252,7 @@
         <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1273,40 +1273,40 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB4" t="n">
         <v>1.15</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
         <v>4.84</v>
@@ -1825,10 +1825,10 @@
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="AE7" t="n">
         <v>1.7</v>
@@ -1852,7 +1852,7 @@
         <v>1.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AM7" t="n">
         <v>1.16</v>
@@ -1979,83 +1979,83 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.75</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
         <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.24</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S16" t="n">
-        <v>3.62</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL16" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AM16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.72</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="BE16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
         <v>3.35</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="AH17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>2.15</v>
       </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="BA17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC17" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="BD17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.56</v>
       </c>
-      <c r="AY17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U19" t="n">
         <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.12</v>
       </c>
       <c r="V19" t="n">
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.85</v>
+        <v>6.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
         <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AS19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BA19" t="n">
         <v>2.08</v>
       </c>
-      <c r="AT19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BB19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BF19" t="n">
         <v>1.16</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,16 +4741,16 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
@@ -4762,13 +4762,13 @@
         <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="X22" t="n">
         <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
         <v>7</v>
@@ -4777,25 +4777,25 @@
         <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
         <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.53</v>
+        <v>3.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AF22" t="n">
         <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
         <v>6.93</v>
@@ -4825,34 +4825,34 @@
         <v>1.28</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AV22" t="n">
         <v>3.08</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
@@ -4938,22 +4938,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="V23" t="n">
         <v>1.35</v>
@@ -4962,16 +4962,16 @@
         <v>2.94</v>
       </c>
       <c r="X23" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
         <v>6.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.05</v>
@@ -4980,37 +4980,37 @@
         <v>1.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AE23" t="n">
         <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG23" t="n">
         <v>2.94</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>1.33</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="BA23" t="n">
         <v>1.71</v>
@@ -5058,13 +5058,13 @@
         <v>2</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="S24" t="n">
         <v>1.85</v>
@@ -5150,16 +5150,16 @@
         <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>8.15</v>
+        <v>8.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
         <v>3.02</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
@@ -5168,7 +5168,7 @@
         <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
         <v>1.04</v>
@@ -5198,7 +5198,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>1.73</v>
@@ -5207,61 +5207,61 @@
         <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5923,22 +5923,22 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="U28" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="V28" t="n">
         <v>1.36</v>
@@ -5947,7 +5947,7 @@
         <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
@@ -5959,37 +5959,37 @@
         <v>1.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>3.44</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK28" t="n">
         <v>1.75</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AM28" t="n">
         <v>1.3</v>
@@ -6007,10 +6007,10 @@
         <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AT28" t="n">
         <v>2.92</v>
@@ -6022,22 +6022,22 @@
         <v>2.53</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AY28" t="n">
         <v>1.31</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
         <v>2.2</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="S2" t="n">
         <v>2.4</v>
@@ -816,7 +816,7 @@
         <v>2.19</v>
       </c>
       <c r="U2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.32</v>
@@ -840,16 +840,16 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
         <v>3.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
         <v>2.81</v>
@@ -861,7 +861,7 @@
         <v>5.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
         <v>1.67</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="T3" t="n">
         <v>2.2</v>
@@ -1049,7 +1049,7 @@
         <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="AH3" t="n">
         <v>1.35</v>
@@ -1058,19 +1058,19 @@
         <v>5.29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
         <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
         <v>3.98</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
         <v>6.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
         <v>4.84</v>
@@ -1825,10 +1825,10 @@
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
         <v>1.7</v>
@@ -1837,7 +1837,7 @@
         <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="AH7" t="n">
         <v>1.39</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.92</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="AZ16" t="n">
         <v>2.15</v>
       </c>
-      <c r="AT16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BA16" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="S17" t="n">
-        <v>3.46</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>2.68</v>
+        <v>3.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="X17" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.300000000000001</v>
+        <v>6.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Q18" t="n">
         <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4153,127 +4153,127 @@
         <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R19" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="n">
         <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AR19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS19" t="n">
         <v>1.91</v>
       </c>
-      <c r="AS19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT19" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>4.58</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="AW19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AX19" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BF19" t="n">
         <v>1.16</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>3.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="R21" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>1.32</v>
@@ -825,7 +825,7 @@
         <v>2.96</v>
       </c>
       <c r="X2" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
         <v>1.42</v>
@@ -855,7 +855,7 @@
         <v>2.81</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" t="n">
         <v>5.1</v>
@@ -867,7 +867,7 @@
         <v>1.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AM2" t="n">
         <v>1.21</v>
@@ -918,7 +918,7 @@
         <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>3.92</v>
@@ -998,40 +998,40 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="T3" t="n">
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
@@ -1040,37 +1040,37 @@
         <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AH3" t="n">
         <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
         <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>6.67</v>
+        <v>5.75</v>
       </c>
       <c r="S7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T7" t="n">
         <v>2.28</v>
@@ -1816,7 +1816,7 @@
         <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
         <v>1.08</v>
@@ -1831,13 +1831,13 @@
         <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
         <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AH7" t="n">
         <v>1.39</v>
@@ -1846,19 +1846,19 @@
         <v>4.97</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
         <v>1.86</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>6.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -3186,7 +3186,7 @@
         <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="X14" t="n">
         <v>2.36</v>
@@ -3231,7 +3231,7 @@
         <v>1.48</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AM14" t="n">
         <v>1.25</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>6.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR16" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AS16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AY16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>1.89</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BA16" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.92</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AZ17" t="n">
         <v>2.15</v>
       </c>
-      <c r="AT17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BA17" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>8.6</v>
+        <v>2.92</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4153,127 +4153,127 @@
         <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
         <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.58</v>
+        <v>3.35</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.05</v>
+        <v>2.43</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BF19" t="n">
         <v>1.16</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>3.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R20" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>2.11</v>
+        <v>8.6</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q4" t="n">
         <v>3.4</v>
@@ -1204,28 +1204,28 @@
         <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
         <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
         <v>1.06</v>
@@ -1237,10 +1237,10 @@
         <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
@@ -1249,7 +1249,7 @@
         <v>2.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
         <v>5.25</v>
@@ -1258,67 +1258,67 @@
         <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.34</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
         <v>2.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
         <v>4.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF4" t="n">
         <v>1.17</v>
@@ -1392,49 +1392,49 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1443,28 +1443,28 @@
         <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>6.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>1.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>2.55</v>
+        <v>8.6</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="S17" t="n">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.41</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z17" t="n">
-        <v>8.300000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU17" t="n">
         <v>3.35</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AV17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW17" t="n">
         <v>1.8</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN17" t="n">
+      <c r="AX17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.34</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AZ17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC17" t="n">
         <v>2</v>
       </c>
-      <c r="AS17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD17" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>3.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.92</v>
+        <v>2.11</v>
       </c>
       <c r="S18" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.33</v>
+        <v>2.58</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AV20" t="n">
         <v>3.05</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.32</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>8.6</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -813,7 +813,7 @@
         <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
         <v>4</v>
@@ -828,7 +828,7 @@
         <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z2" t="n">
         <v>5.9</v>
@@ -840,7 +840,7 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AD2" t="n">
         <v>3.58</v>
@@ -855,13 +855,13 @@
         <v>2.81</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>5.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
         <v>1.67</v>
@@ -873,7 +873,7 @@
         <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.93</v>
+        <v>4.11</v>
       </c>
       <c r="T3" t="n">
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1028,7 +1028,7 @@
         <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
         <v>1.08</v>
@@ -1055,10 +1055,10 @@
         <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
         <v>1.65</v>
@@ -1070,7 +1070,7 @@
         <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1237,22 +1237,22 @@
         <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
         <v>1.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.09</v>
@@ -1264,46 +1264,46 @@
         <v>2.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AS4" t="n">
         <v>2.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AX4" t="n">
         <v>1.67</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BA4" t="n">
         <v>2.15</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
@@ -1437,16 +1437,16 @@
         <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" t="n">
         <v>6.3</v>
@@ -1455,16 +1455,16 @@
         <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
         <v>1.15</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>2.95</v>
@@ -1613,10 +1613,10 @@
         <v>2.39</v>
       </c>
       <c r="X6" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
         <v>7.9</v>
@@ -1637,13 +1637,13 @@
         <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
         <v>7.1</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC6" t="n">
         <v>2.26</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="BE6" t="n">
         <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>4.2</v>
@@ -1810,13 +1810,13 @@
         <v>2.96</v>
       </c>
       <c r="X7" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA7" t="n">
         <v>1.08</v>
@@ -1825,34 +1825,34 @@
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AE7" t="n">
         <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.97</v>
+        <v>4.65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
         <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AM7" t="n">
         <v>1.15</v>
@@ -1903,13 +1903,13 @@
         <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BD7" t="n">
         <v>4.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
         <v>1.21</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>1.32</v>
@@ -2007,7 +2007,7 @@
         <v>2.96</v>
       </c>
       <c r="X8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Y8" t="n">
         <v>1.44</v>
@@ -2025,25 +2025,25 @@
         <v>1.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
         <v>1.64</v>
@@ -2052,7 +2052,7 @@
         <v>2.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN8" t="n">
         <v>1.85</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BD8" t="n">
         <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BF8" t="n">
         <v>1.19</v>
@@ -2176,83 +2176,83 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
         <v>3.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
         <v>1.7</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,16 +2294,16 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF9" t="n">
         <v>1.17</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.6</v>
+        <v>10.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>5.9</v>
+        <v>7.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AD11" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>6.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>4.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.55</v>
+        <v>8.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
         <v>3.05</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.92</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>3.68</v>
+        <v>8.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="X19" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BF19" t="n">
         <v>1.2</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
         <v>1.24</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW20" t="n">
         <v>1.92</v>
       </c>
-      <c r="AG20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AX20" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4550,46 +4550,46 @@
         <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="X21" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
         <v>1.7</v>
@@ -4598,25 +4598,25 @@
         <v>3.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,49 +4625,49 @@
         <v>1.35</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AT21" t="n">
         <v>3.35</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AY21" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
         <v>1.1</v>
@@ -4741,16 +4741,16 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
@@ -4759,34 +4759,34 @@
         <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="X22" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA22" t="n">
         <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
         <v>1.8</v>
@@ -4798,13 +4798,13 @@
         <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL22" t="n">
         <v>1.91</v>
@@ -4819,40 +4819,40 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
@@ -4867,7 +4867,7 @@
         <v>1.62</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4938,46 +4938,46 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
         <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="X23" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB23" t="n">
         <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD23" t="n">
         <v>3.54</v>
@@ -4986,28 +4986,28 @@
         <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
         <v>2.94</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AN23" t="n">
         <v>1.36</v>
@@ -5016,55 +5016,55 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="AV23" t="n">
         <v>2.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BA23" t="n">
         <v>1.71</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,73 +5135,73 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="R24" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
         <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>8.08</v>
+        <v>5.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="X24" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
         <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
@@ -5216,52 +5216,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AT24" t="n">
         <v>2.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.58</v>
+        <v>3.49</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.65</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5923,19 +5923,19 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="T28" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
         <v>4.25</v>
@@ -5947,40 +5947,40 @@
         <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.08</v>
@@ -5989,10 +5989,10 @@
         <v>1.75</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
         <v>1.73</v>
@@ -6004,52 +6004,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.58</v>
+        <v>3.49</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AW28" t="n">
         <v>1.89</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BA28" t="n">
         <v>2.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC28" t="n">
         <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="BE28" t="n">
         <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="T2" t="n">
         <v>2.34</v>
@@ -828,7 +828,7 @@
         <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
         <v>5.9</v>
@@ -843,13 +843,13 @@
         <v>1.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG2" t="n">
         <v>2.81</v>
@@ -873,46 +873,46 @@
         <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="BB2" t="n">
         <v>1.18</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>4.13</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
         <v>4.11</v>
@@ -1016,19 +1016,19 @@
         <v>2.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AA3" t="n">
         <v>1.08</v>
@@ -1043,7 +1043,7 @@
         <v>3.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -1052,7 +1052,7 @@
         <v>2.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>5.37</v>
@@ -1064,7 +1064,7 @@
         <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AM3" t="n">
         <v>1.2</v>
@@ -1076,40 +1076,40 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB3" t="n">
         <v>1.17</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
         <v>1.98</v>
@@ -1828,10 +1828,10 @@
         <v>1.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
         <v>2</v>
@@ -1840,64 +1840,64 @@
         <v>2.72</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
         <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="BB7" t="n">
         <v>1.16</v>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R8" t="n">
         <v>4.3</v>
@@ -2007,10 +2007,10 @@
         <v>2.96</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
         <v>5.7</v>
@@ -2019,7 +2019,7 @@
         <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
         <v>1.19</v>
@@ -2031,7 +2031,7 @@
         <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AG8" t="n">
         <v>2.69</v>
@@ -2189,13 +2189,13 @@
         <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
@@ -2207,10 +2207,10 @@
         <v>2.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
         <v>1.06</v>
@@ -2219,19 +2219,19 @@
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AE9" t="n">
         <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.33</v>
@@ -2243,7 +2243,7 @@
         <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AL9" t="n">
         <v>1.95</v>
@@ -2252,49 +2252,49 @@
         <v>1.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.5</v>
+        <v>18.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.34</v>
+        <v>10.43</v>
       </c>
       <c r="R10" t="n">
         <v>1.08</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R11" t="n">
-        <v>7.48</v>
+        <v>6.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="T11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>5.6</v>
+        <v>7.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="X11" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="Q12" t="n">
         <v>3.85</v>
       </c>
       <c r="R12" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z12" t="n">
         <v>6.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AA12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>6.25</v>
+        <v>6.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>4.29</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="X14" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
         <v>1.91</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>4.29</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>3.16</v>
+        <v>2.44</v>
       </c>
       <c r="X16" t="n">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
-        <v>4.29</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.45</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
         <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.38</v>
       </c>
-      <c r="AI18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM18" t="n">
+      <c r="AN18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>8.75</v>
+        <v>3.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>2.71</v>
+        <v>2.91</v>
       </c>
       <c r="X19" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>3</v>
       </c>
       <c r="AH19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,130 +4347,130 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>1.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="R20" t="n">
-        <v>2.88</v>
+        <v>7.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
-        <v>3.66</v>
+        <v>8.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AN20" t="n">
-        <v>1.53</v>
+        <v>2.82</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AW20" t="n">
         <v>1.92</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BF20" t="n">
         <v>1.2</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="S8" t="n">
-        <v>2.29</v>
+        <v>4.74</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
         <v>3.85</v>
       </c>
       <c r="R11" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z11" t="n">
         <v>6.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="AA11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
         <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>6.52</v>
+        <v>6.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>5.6</v>
+        <v>7.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="X12" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,83 +3161,83 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="R14" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,83 +3358,83 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
         <v>2.45</v>
@@ -3774,10 +3774,10 @@
         <v>3.05</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
         <v>2.53</v>
@@ -3795,7 +3795,7 @@
         <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
         <v>3.7</v>
@@ -3819,10 +3819,10 @@
         <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
         <v>1.29</v>
@@ -3837,7 +3837,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR17" t="n">
         <v>1.74</v>
@@ -3870,7 +3870,7 @@
         <v>2.04</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC17" t="n">
         <v>2.02</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,130 +3953,130 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>1.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="R18" t="n">
-        <v>2.88</v>
+        <v>7.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="U18" t="n">
-        <v>3.66</v>
+        <v>8.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X18" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AN18" t="n">
-        <v>1.53</v>
+        <v>2.82</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AW18" t="n">
         <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BF18" t="n">
         <v>1.2</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI19" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AM19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,130 +4347,130 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>7.87</v>
+        <v>2.88</v>
       </c>
       <c r="S20" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>8.4</v>
+        <v>3.66</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU20" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.52</v>
-      </c>
       <c r="AV20" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AW20" t="n">
         <v>1.92</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BF20" t="n">
         <v>1.2</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.95</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="X21" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.04</v>
+        <v>3.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AN21" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.14</v>
+        <v>12.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.43</v>
+        <v>9.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.08</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.1</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.29</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.45</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH16" t="n">
+      <c r="AZ16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,40 +3756,40 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="R17" t="n">
-        <v>2.45</v>
+        <v>7.87</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="U17" t="n">
-        <v>3.05</v>
+        <v>8.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="X17" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
@@ -3798,91 +3798,91 @@
         <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
         <v>1.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.09</v>
       </c>
       <c r="AK17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.49</v>
+        <v>2.82</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,130 +3953,130 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>7.87</v>
+        <v>2.88</v>
       </c>
       <c r="S18" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>8.4</v>
+        <v>3.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU18" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.52</v>
-      </c>
       <c r="AV18" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AW18" t="n">
         <v>1.92</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
         <v>1.2</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>4.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="U19" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="V19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.36</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AD19" t="n">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AN19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.28</v>
       </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC19" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="BF19" t="n">
         <v>1.1</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD21" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI21" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AM21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,7 +4744,7 @@
         <v>3.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
         <v>2.05</v>
@@ -4756,22 +4756,22 @@
         <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="X22" t="n">
         <v>2.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.04</v>
@@ -4789,7 +4789,7 @@
         <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
         <v>3.4</v>
@@ -4798,10 +4798,10 @@
         <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.91</v>
+        <v>7.13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
         <v>1.76</v>
@@ -4810,7 +4810,7 @@
         <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AN22" t="n">
         <v>1.3</v>
@@ -4819,37 +4819,37 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.27</v>
+        <v>4.55</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BA22" t="n">
         <v>1.65</v>
@@ -4858,13 +4858,13 @@
         <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BD22" t="n">
         <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
         <v>1.14</v>
@@ -4938,34 +4938,34 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="X23" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
         <v>6</v>
@@ -4977,7 +4977,7 @@
         <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
         <v>3.54</v>
@@ -4992,13 +4992,13 @@
         <v>2.94</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
         <v>1.65</v>
@@ -5007,7 +5007,7 @@
         <v>2.08</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
         <v>1.36</v>
@@ -5016,40 +5016,40 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AY23" t="n">
         <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="BB23" t="n">
         <v>1.2</v>
@@ -5064,7 +5064,7 @@
         <v>1.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,37 +5135,37 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
         <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
         <v>5.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
@@ -5174,22 +5174,22 @@
         <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AE24" t="n">
         <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG24" t="n">
         <v>2.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
         <v>5.75</v>
@@ -5207,7 +5207,7 @@
         <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>2.17</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AU24" t="n">
         <v>3.49</v>
@@ -5240,7 +5240,7 @@
         <v>1.61</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.27</v>
@@ -5252,13 +5252,13 @@
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BF24" t="n">
         <v>1.17</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
         <v>3.6</v>
@@ -5938,7 +5938,7 @@
         <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.36</v>
@@ -5947,13 +5947,13 @@
         <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
         <v>1.03</v>
@@ -5962,19 +5962,19 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD28" t="n">
         <v>3.35</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AH28" t="n">
         <v>1.23</v>
@@ -5995,7 +5995,7 @@
         <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,16 +6004,16 @@
         <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AS28" t="n">
         <v>2.17</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AU28" t="n">
         <v>3.49</v>
@@ -6022,19 +6022,19 @@
         <v>2.57</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AX28" t="n">
         <v>1.61</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
@@ -6043,13 +6043,13 @@
         <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
         <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
@@ -1407,7 +1407,7 @@
         <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
@@ -1419,7 +1419,7 @@
         <v>2.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
         <v>6.7</v>
@@ -1437,10 +1437,10 @@
         <v>3.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
         <v>3.2</v>
@@ -1458,13 +1458,13 @@
         <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="BD5" t="n">
         <v>3.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,40 +1589,40 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="X6" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
         <v>1.04</v>
@@ -1646,22 +1646,22 @@
         <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.04</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
         <v>2.26</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
         <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
       <c r="BE8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>2.29</v>
+        <v>4.74</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>12.74</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
         <v>9.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,80 +2968,80 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>6.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="S13" t="n">
-        <v>7.42</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="X13" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
         <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.25</v>
+        <v>4.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,35 +3358,35 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.19</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="X15" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
         <v>1.55</v>
@@ -3395,100 +3395,100 @@
         <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="AQ15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>4.29</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="X16" t="n">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>3.66</v>
+        <v>2.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X18" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.75</v>
+        <v>8.1</v>
       </c>
       <c r="AA18" t="n">
         <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN18" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AY18" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S19" t="n">
-        <v>4.29</v>
+        <v>2.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>2.79</v>
+        <v>3.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AI19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX19" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.14</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.95</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="X21" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AN21" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,13 +4744,13 @@
         <v>3.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
         <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
         <v>2.1</v>
@@ -4759,28 +4759,28 @@
         <v>2.45</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="X22" t="n">
         <v>2.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AA22" t="n">
         <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
         <v>3.3</v>
@@ -4789,28 +4789,28 @@
         <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
         <v>3.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.13</v>
+        <v>6.55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AL22" t="n">
         <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
         <v>1.3</v>
@@ -4819,34 +4819,34 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AU22" t="n">
         <v>4.55</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.48</v>
@@ -4858,16 +4858,16 @@
         <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BD22" t="n">
         <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4938,16 +4938,16 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="T23" t="n">
         <v>2.2</v>
@@ -4956,16 +4956,16 @@
         <v>2.63</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="X23" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z23" t="n">
         <v>6</v>
@@ -4977,34 +4977,34 @@
         <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AH23" t="n">
         <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AM23" t="n">
         <v>1.3</v>
@@ -5019,28 +5019,28 @@
         <v>1.24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
         <v>1.74</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AT23" t="n">
         <v>2.82</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AV23" t="n">
         <v>2.57</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AY23" t="n">
         <v>1.38</v>
@@ -5055,16 +5055,16 @@
         <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="BE23" t="n">
         <v>1.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
         <v>1.85</v>
@@ -5153,13 +5153,13 @@
         <v>5.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="X24" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
         <v>1.44</v>
@@ -5177,7 +5177,7 @@
         <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AE24" t="n">
         <v>1.88</v>
@@ -5192,7 +5192,7 @@
         <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.13</v>
@@ -5207,61 +5207,61 @@
         <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.49</v>
+        <v>3.68</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="BD24" t="n">
         <v>4.05</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="S28" t="n">
         <v>2.61</v>
@@ -5938,7 +5938,7 @@
         <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V28" t="n">
         <v>1.36</v>
@@ -5947,13 +5947,13 @@
         <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1.03</v>
@@ -5962,22 +5962,22 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" t="n">
         <v>6.95</v>
@@ -5989,52 +5989,52 @@
         <v>1.75</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AS28" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
@@ -6046,10 +6046,10 @@
         <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -804,25 +804,25 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="S2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.35</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X2" t="n">
         <v>2.4</v>
@@ -840,28 +840,28 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
         <v>1.67</v>
@@ -873,13 +873,13 @@
         <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.69</v>
@@ -888,13 +888,13 @@
         <v>2.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AT2" t="n">
         <v>3.99</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AV2" t="n">
         <v>2.04</v>
@@ -903,7 +903,7 @@
         <v>1.63</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AY2" t="n">
         <v>1.16</v>
@@ -924,10 +924,10 @@
         <v>3.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>4.11</v>
+        <v>4.37</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U3" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
         <v>1.28</v>
@@ -1025,7 +1025,7 @@
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
         <v>5.7</v>
@@ -1040,10 +1040,10 @@
         <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.72</v>
+        <v>3.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -1052,10 +1052,10 @@
         <v>2.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.1</v>
@@ -1067,10 +1067,10 @@
         <v>2.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AR3" t="n">
         <v>2.68</v>
@@ -1091,7 +1091,7 @@
         <v>4.31</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AV3" t="n">
         <v>1.96</v>
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="U4" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA4" t="n">
         <v>1.06</v>
@@ -1237,37 +1237,37 @@
         <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
         <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>1.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AU4" t="n">
         <v>4.09</v>
@@ -1297,7 +1297,7 @@
         <v>2.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AY4" t="n">
         <v>1.4</v>
@@ -1309,19 +1309,19 @@
         <v>2.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1789,13 +1789,13 @@
         <v>1.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
         <v>2.28</v>
@@ -1804,82 +1804,82 @@
         <v>4.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2.72</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AS7" t="n">
         <v>2.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AV7" t="n">
         <v>2.38</v>
@@ -1891,28 +1891,28 @@
         <v>1.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.19</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
         <v>4.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V8" t="n">
         <v>1.32</v>
@@ -2010,7 +2010,7 @@
         <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
         <v>5.7</v>
@@ -2022,7 +2022,7 @@
         <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
         <v>3.74</v>
@@ -2040,13 +2040,13 @@
         <v>1.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL8" t="n">
         <v>2.1</v>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
         <v>1.92</v>
@@ -2106,7 +2106,7 @@
         <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF8" t="n">
         <v>1.19</v>
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
@@ -2204,100 +2204,100 @@
         <v>2.91</v>
       </c>
       <c r="X9" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AH9" t="n">
         <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>1.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BB9" t="n">
         <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
         <v>4</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
         <v>3.85</v>
       </c>
       <c r="R11" t="n">
-        <v>6.52</v>
+        <v>6.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="T11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>5.6</v>
+        <v>7.46</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="X11" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK11" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,37 +2771,37 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U12" t="n">
-        <v>7.75</v>
+        <v>5.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AA12" t="n">
         <v>1.06</v>
@@ -2810,40 +2810,40 @@
         <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
         <v>3.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
         <v>1.14</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X13" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,31 +3362,31 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>6.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>2.19</v>
       </c>
       <c r="S15" t="n">
-        <v>6.5</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="Y15" t="n">
         <v>1.55</v>
@@ -3395,100 +3395,100 @@
         <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.49</v>
+        <v>4.26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.94</v>
       </c>
-      <c r="AX15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BF15" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,28 +3559,28 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S16" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="X16" t="n">
         <v>3.14</v>
@@ -3589,7 +3589,7 @@
         <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AA16" t="n">
         <v>1.03</v>
@@ -3598,40 +3598,40 @@
         <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AF16" t="n">
         <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AH16" t="n">
         <v>1.16</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AM16" t="n">
         <v>1.28</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>7.87</v>
+        <v>6.5</v>
       </c>
       <c r="S17" t="n">
         <v>1.87</v>
       </c>
       <c r="T17" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>8.4</v>
+        <v>7.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="X17" t="n">
         <v>2.55</v>
@@ -3786,10 +3786,10 @@
         <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
@@ -3798,37 +3798,37 @@
         <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.19</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="BD17" t="n">
         <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="S18" t="n">
         <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="X18" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
         <v>3.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL18" t="n">
         <v>2.05</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>1.35</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AT18" t="n">
         <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AY18" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC18" t="n">
         <v>2.17</v>
       </c>
-      <c r="BA18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="R19" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT19" t="n">
         <v>2.85</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AU19" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>3.82</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X20" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AM20" t="n">
         <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS20" t="n">
         <v>2.15</v>
       </c>
-      <c r="AS20" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AT20" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -4562,22 +4562,22 @@
         <v>3.05</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X21" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
         <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
         <v>1.01</v>
@@ -4586,88 +4586,88 @@
         <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK21" t="n">
         <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="AS21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AT21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="BB21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC21" t="n">
         <v>1.97</v>
       </c>
-      <c r="AX21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.01</v>
-      </c>
       <c r="BD21" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BF21" t="n">
         <v>1.16</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="S2" t="n">
         <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -840,10 +840,10 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
@@ -852,28 +852,28 @@
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
         <v>1.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
         <v>2.52</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AT2" t="n">
         <v>3.99</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AV2" t="n">
         <v>2.04</v>
@@ -903,7 +903,7 @@
         <v>1.63</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AY2" t="n">
         <v>1.16</v>
@@ -915,19 +915,19 @@
         <v>4.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="R3" t="n">
         <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="T3" t="n">
         <v>2.21</v>
@@ -1028,10 +1028,10 @@
         <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
@@ -1040,22 +1040,22 @@
         <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.1</v>
@@ -1064,7 +1064,7 @@
         <v>1.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AM3" t="n">
         <v>1.19</v>
@@ -1091,7 +1091,7 @@
         <v>4.31</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AV3" t="n">
         <v>1.96</v>
@@ -1115,13 +1115,13 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
         <v>1.18</v>
@@ -1786,73 +1786,73 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
         <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>4.84</v>
+        <v>5.03</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="X7" t="n">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.31</v>
+        <v>5.09</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AM7" t="n">
         <v>1.14</v>
@@ -1900,19 +1900,19 @@
         <v>4.65</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>3.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>4.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>3.9</v>
+        <v>2.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="X8" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
         <v>1.04</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB8" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC8" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.75</v>
+        <v>4.3</v>
       </c>
       <c r="S9" t="n">
-        <v>4.73</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.29</v>
+        <v>3.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="X9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
         <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.3</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.42</v>
       </c>
-      <c r="S13" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>5.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.95</v>
+        <v>5.58</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="X15" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.2</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.12</v>
+        <v>6.5</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="T16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.92</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AX16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4.2</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="BE16" t="n">
         <v>1.7</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="S17" t="n">
-        <v>1.87</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>7.85</v>
+        <v>3.64</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="X17" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AN17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AR17" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.52</v>
+        <v>2.97</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AW17" t="n">
         <v>1.92</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="X18" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.8</v>
+        <v>5.46</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
         <v>1.33</v>
       </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AR18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA18" t="n">
         <v>2.17</v>
       </c>
-      <c r="AS18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="U19" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS19" t="n">
+      <c r="AZ19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC19" t="n">
         <v>2.17</v>
       </c>
-      <c r="AT19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.01</v>
-      </c>
       <c r="BD19" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
         <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.85</v>
+        <v>5.42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.34</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>3.82</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>2.91</v>
+        <v>2.41</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -772,32 +772,32 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -969,96 +969,96 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S3" t="n">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="T3" t="n">
         <v>2.21</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AE3" t="n">
         <v>1.71</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.5</v>
+        <v>5.39</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
         <v>1.65</v>
@@ -1070,7 +1070,7 @@
         <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,13 +1115,13 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
         <v>1.18</v>
@@ -1166,51 +1166,51 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="U4" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1219,55 +1219,55 @@
         <v>3.23</v>
       </c>
       <c r="X4" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.05</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
         <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AM4" t="n">
         <v>1.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AU4" t="n">
         <v>4.09</v>
@@ -1297,7 +1297,7 @@
         <v>2.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AY4" t="n">
         <v>1.4</v>
@@ -1312,13 +1312,13 @@
         <v>1.14</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BF4" t="n">
         <v>1.18</v>
@@ -1363,108 +1363,108 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.26</v>
+        <v>3.06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1575,93 +1575,93 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.95</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="T6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.9</v>
       </c>
-      <c r="U6" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AL6" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1775,14 +1775,14 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1792,73 +1792,73 @@
         <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="S7" t="n">
         <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>5.03</v>
+        <v>5.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
         <v>1.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.09</v>
+        <v>4.84</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AL7" t="n">
         <v>1.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AS7" t="n">
         <v>2.33</v>
@@ -1900,19 +1900,19 @@
         <v>4.65</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1972,90 +1972,90 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="T8" t="n">
         <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="X8" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="AA8" t="n">
         <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2067,13 +2067,13 @@
         <v>1.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AS8" t="n">
         <v>2.19</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AU8" t="n">
         <v>3.64</v>
@@ -2088,13 +2088,13 @@
         <v>1.59</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
         <v>3.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BB8" t="n">
         <v>1.22</v>
@@ -2103,13 +2103,13 @@
         <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2169,48 +2169,48 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R9" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
         <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="X9" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1.08</v>
@@ -2222,37 +2222,37 @@
         <v>1.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,16 +2297,16 @@
         <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2351,39 +2351,39 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2563,72 +2563,72 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>3.69</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="S11" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>7.46</v>
+        <v>7.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="X11" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
         <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
@@ -2637,16 +2637,16 @@
         <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
         <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BD11" t="n">
         <v>3.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -2760,30 +2760,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>5.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
         <v>5.6</v>
@@ -2834,16 +2834,16 @@
         <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AM12" t="n">
         <v>1.03</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2954,33 +2954,33 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>2.8</v>
@@ -2989,7 +2989,7 @@
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="X13" t="n">
         <v>2.28</v>
@@ -3004,13 +3004,13 @@
         <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
         <v>1.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.52</v>
@@ -3019,13 +3019,13 @@
         <v>2.26</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="n">
         <v>1.52</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.26</v>
+        <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.16</v>
@@ -3040,7 +3040,7 @@
         <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>1.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BD13" t="n">
         <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BF13" t="n">
         <v>1.25</v>
@@ -3127,171 +3127,171 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q14" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU14" t="n">
         <v>3.48</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,117 +3324,117 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>5.58</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
         <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>2.11</v>
+        <v>2.84</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3446,22 +3446,22 @@
         <v>1.46</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AX15" t="n">
         <v>1.55</v>
@@ -3470,25 +3470,25 @@
         <v>1.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="BA15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.27</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3533,13 +3533,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -3548,51 +3548,51 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="S16" t="n">
         <v>1.87</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>7.85</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="X16" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
@@ -3601,37 +3601,37 @@
         <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
         <v>2.25</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AM16" t="n">
         <v>1.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,171 +3718,171 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU17" t="n">
         <v>3.05</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AV17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI17" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,25 +3915,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -3942,144 +3942,144 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC18" t="n">
         <v>2.25</v>
       </c>
-      <c r="U18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BD18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BE18" t="n">
         <v>1.48</v>
       </c>
-      <c r="AY18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF18" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,16 +4112,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -4133,150 +4133,150 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL19" t="n">
+      <c r="AZ19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC19" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BD19" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,19 +4309,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4330,150 +4330,150 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="X20" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA20" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.95</v>
       </c>
       <c r="BB20" t="n">
         <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,171 +4506,171 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="T21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW21" t="n">
         <v>1.92</v>
       </c>
-      <c r="U21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AX21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY21" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,130 +4741,130 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q22" t="n">
         <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="X22" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Y22" t="n">
         <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
         <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AL22" t="n">
         <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AX22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.65</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BF22" t="n">
         <v>1.17</v>
@@ -4944,127 +4944,127 @@
         <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="X23" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.1</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AW23" t="n">
         <v>1.98</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AZ23" t="n">
         <v>2.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BB23" t="n">
         <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,40 +5135,40 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U24" t="n">
-        <v>5.9</v>
+        <v>6.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
         <v>1</v>
@@ -5177,31 +5177,31 @@
         <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.6</v>
+        <v>4.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
         <v>2.01</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
@@ -5225,43 +5225,43 @@
         <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
         <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5923,118 +5923,118 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="X28" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI28" t="n">
-        <v>6.95</v>
+        <v>6.55</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.08</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
@@ -6043,13 +6043,13 @@
         <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>

--- a/jogos_2026-03-12.xlsx
+++ b/jogos_2026-03-12.xlsx
@@ -1945,22 +1945,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>4.35</v>
       </c>
       <c r="S8" t="n">
-        <v>4.78</v>
+        <v>2.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="V8" t="n">
         <v>1.31</v>
@@ -2007,109 +2007,109 @@
         <v>3.02</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.05</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="BD8" t="n">
         <v>4.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,22 +2142,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2180,22 +2180,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>4.35</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>4.78</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.31</v>
@@ -2204,109 +2204,109 @@
         <v>3.02</v>
       </c>
       <c r="X9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55</v>
+        <v>6.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.59</v>
       </c>
-      <c r="AL9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AY9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC9" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
         <v>4.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2930,171 +2930,171 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM13" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AN13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,117 +3127,117 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.56</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.27</v>
       </c>
-      <c r="U14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.65</v>
+        <v>3.88</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,25 +3246,25 @@
         <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AX14" t="n">
         <v>1.55</v>
@@ -3273,25 +3273,25 @@
         <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="BA14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.27</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,37 +3324,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.21</v>
-      </c>
       <c r="U15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="X15" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="BC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD15" t="n">
         <v>4.9</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE15" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,37 +3521,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>6.75</v>
+        <v>2.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.87</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X16" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF16" t="n">
         <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,37 +3718,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U17" t="n">
         <v>3.2</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Y17" t="n">
         <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA17" t="n">
         <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS17" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.48</v>
       </c>
       <c r="AT17" t="n">
         <v>3.23</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AV17" t="n">
         <v>2.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
         <v>1.28</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,22 +3915,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -3942,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG18" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.56</v>
       </c>
-      <c r="AG18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN18" t="n">
+      <c r="AY18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,37 +4309,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>3</v>
-      </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AR20" t="n">
         <v>1.85</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,171 +4506,171 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>5</v>
       </c>
       <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="S21" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z21" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AD21" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="AE21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.9</v>
       </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AL21" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.28</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV21" t="n">
+      <c r="BC21" t="n">
         <v>2.25</v>
       </c>
-      <c r="AW21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD21" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,31 +4744,31 @@
         <v>3.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
         <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
         <v>7</v>
@@ -4786,13 +4786,13 @@
         <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
         <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AH22" t="n">
         <v>1.28</v>
@@ -4804,13 +4804,13 @@
         <v>1.07</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL22" t="n">
         <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="AN22" t="n">
         <v>1.25</v>
@@ -4831,10 +4831,10 @@
         <v>1.88</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV22" t="n">
         <v>3.05</v>
@@ -4849,7 +4849,7 @@
         <v>1.48</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="BA22" t="n">
         <v>1.73</v>
@@ -4861,7 +4861,7 @@
         <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BE22" t="n">
         <v>1.67</v>
@@ -4938,16 +4938,16 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
         <v>2.1</v>
@@ -4956,16 +4956,16 @@
         <v>2.82</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="X23" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
         <v>6.5</v>
@@ -4980,7 +4980,7 @@
         <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AE23" t="n">
         <v>1.91</v>
@@ -4989,16 +4989,16 @@
         <v>1.92</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.52</v>
+        <v>6.79</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
         <v>1.67</v>
@@ -5022,7 +5022,7 @@
         <v>1.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AS23" t="n">
         <v>2.16</v>
@@ -5037,7 +5037,7 @@
         <v>2.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AX23" t="n">
         <v>1.57</v>
@@ -5049,7 +5049,7 @@
         <v>2.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BB23" t="n">
         <v>1.2</v>
@@ -5061,10 +5061,10 @@
         <v>3.88</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="R24" t="n">
         <v>7</v>
@@ -5147,22 +5147,22 @@
         <v>1.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U24" t="n">
         <v>6.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X24" t="n">
         <v>2.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
         <v>6.1</v>
@@ -5174,13 +5174,13 @@
         <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF24" t="n">
         <v>2.01</v>
@@ -5189,25 +5189,25 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
         <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5246,22 +5246,22 @@
         <v>1.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5941,10 +5941,10 @@
         <v>3.75</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="X28" t="n">
         <v>2.81</v>
@@ -5962,22 +5962,22 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI28" t="n">
         <v>6.55</v>
@@ -5995,7 +5995,7 @@
         <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6034,22 +6034,22 @@
         <v>1.65</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BB28" t="n">
         <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
